--- a/Team-Data/2012-13/12-30-2012-13.xlsx
+++ b/Team-Data/2012-13/12-30-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>2.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -784,7 +851,7 @@
         <v>25</v>
       </c>
       <c r="AS2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT2" t="n">
         <v>23</v>
@@ -796,7 +863,7 @@
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX2" t="n">
         <v>21</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" t="n">
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>0.467</v>
+        <v>0.483</v>
       </c>
       <c r="H3" t="n">
         <v>49</v>
@@ -861,55 +928,55 @@
         <v>36.7</v>
       </c>
       <c r="J3" t="n">
-        <v>79.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M3" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.348</v>
+        <v>0.35</v>
       </c>
       <c r="O3" t="n">
         <v>17</v>
       </c>
       <c r="P3" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.796</v>
+        <v>0.793</v>
       </c>
       <c r="R3" t="n">
         <v>7.9</v>
       </c>
       <c r="S3" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="T3" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="U3" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="V3" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W3" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z3" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA3" t="n">
         <v>19.7</v>
@@ -918,16 +985,16 @@
         <v>95.90000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>-2.2</v>
+        <v>-1.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
         <v>18</v>
       </c>
       <c r="AF3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG3" t="n">
         <v>19</v>
@@ -939,7 +1006,7 @@
         <v>16</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK3" t="n">
         <v>6</v>
@@ -951,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="AN3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO3" t="n">
         <v>16</v>
       </c>
       <c r="AP3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ3" t="n">
         <v>4</v>
@@ -975,7 +1042,7 @@
         <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW3" t="n">
         <v>8</v>
@@ -984,19 +1051,19 @@
         <v>28</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ3" t="n">
         <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BB3" t="n">
         <v>17</v>
       </c>
       <c r="BC3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>0.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
         <v>11</v>
@@ -1121,10 +1188,10 @@
         <v>28</v>
       </c>
       <c r="AJ4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>12</v>
@@ -1136,10 +1203,10 @@
         <v>23</v>
       </c>
       <c r="AO4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
         <v>21</v>
@@ -1154,7 +1221,7 @@
         <v>20</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV4" t="n">
         <v>6</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-9</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
         <v>27</v>
@@ -1336,7 +1403,7 @@
         <v>18</v>
       </c>
       <c r="AU5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV5" t="n">
         <v>5</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>1.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE6" t="n">
         <v>11</v>
@@ -1488,7 +1555,7 @@
         <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL6" t="n">
         <v>30</v>
@@ -1497,7 +1564,7 @@
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO6" t="n">
         <v>7</v>
@@ -1515,7 +1582,7 @@
         <v>12</v>
       </c>
       <c r="AT6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
@@ -1679,13 +1746,13 @@
         <v>9</v>
       </c>
       <c r="AN7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO7" t="n">
         <v>24</v>
       </c>
       <c r="AP7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ7" t="n">
         <v>22</v>
@@ -1724,7 +1791,7 @@
         <v>24</v>
       </c>
       <c r="BC7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -1753,61 +1820,61 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
         <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G8" t="n">
-        <v>0.387</v>
+        <v>0.4</v>
       </c>
       <c r="H8" t="n">
         <v>49</v>
       </c>
       <c r="I8" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J8" t="n">
-        <v>83.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="K8" t="n">
-        <v>0.446</v>
+        <v>0.448</v>
       </c>
       <c r="L8" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="M8" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.352</v>
+        <v>0.36</v>
       </c>
       <c r="O8" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="P8" t="n">
-        <v>21.8</v>
+        <v>22.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.784</v>
+        <v>0.782</v>
       </c>
       <c r="R8" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="S8" t="n">
         <v>31.8</v>
       </c>
       <c r="T8" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="U8" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V8" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="W8" t="n">
         <v>8</v>
@@ -1816,31 +1883,31 @@
         <v>5.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z8" t="n">
         <v>21.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="AB8" t="n">
-        <v>98.3</v>
+        <v>98.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>-4.8</v>
+        <v>-4.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
         <v>21</v>
       </c>
       <c r="AF8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH8" t="n">
         <v>2</v>
@@ -1849,25 +1916,25 @@
         <v>11</v>
       </c>
       <c r="AJ8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AK8" t="n">
         <v>14</v>
       </c>
       <c r="AL8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AM8" t="n">
         <v>14</v>
       </c>
       <c r="AN8" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AO8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ8" t="n">
         <v>8</v>
@@ -1879,7 +1946,7 @@
         <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU8" t="n">
         <v>16</v>
@@ -1888,22 +1955,22 @@
         <v>27</v>
       </c>
       <c r="AW8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX8" t="n">
         <v>14</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>13</v>
       </c>
       <c r="AY8" t="n">
         <v>7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC8" t="n">
         <v>25</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>1.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>9</v>
@@ -2046,10 +2113,10 @@
         <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
         <v>30</v>
@@ -2076,10 +2143,10 @@
         <v>4</v>
       </c>
       <c r="AY9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
         <v>4</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -2117,61 +2184,61 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
         <v>22</v>
       </c>
       <c r="G10" t="n">
-        <v>0.333</v>
+        <v>0.313</v>
       </c>
       <c r="H10" t="n">
         <v>48.6</v>
       </c>
       <c r="I10" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J10" t="n">
         <v>81.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L10" t="n">
         <v>6.3</v>
       </c>
       <c r="M10" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0.381</v>
+        <v>0.383</v>
       </c>
       <c r="O10" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P10" t="n">
-        <v>23.8</v>
+        <v>24.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.72</v>
+        <v>0.719</v>
       </c>
       <c r="R10" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="S10" t="n">
         <v>30.9</v>
       </c>
       <c r="T10" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U10" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="W10" t="n">
         <v>6</v>
@@ -2180,25 +2247,25 @@
         <v>5.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB10" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.7</v>
+        <v>-1.8</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF10" t="n">
         <v>26</v>
@@ -2210,13 +2277,13 @@
         <v>10</v>
       </c>
       <c r="AI10" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ10" t="n">
         <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AL10" t="n">
         <v>22</v>
@@ -2231,46 +2298,46 @@
         <v>11</v>
       </c>
       <c r="AP10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ10" t="n">
         <v>27</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AS10" t="n">
         <v>14</v>
       </c>
       <c r="AT10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV10" t="n">
         <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BA10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB10" t="n">
         <v>22</v>
       </c>
       <c r="BC10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>2.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>4</v>
@@ -2410,13 +2477,13 @@
         <v>5</v>
       </c>
       <c r="AO11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
         <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR11" t="n">
         <v>14</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>1.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
         <v>11</v>
@@ -2589,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
         <v>3</v>
@@ -2598,7 +2665,7 @@
         <v>3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR12" t="n">
         <v>21</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -2741,16 +2808,16 @@
         <v>1.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
         <v>9</v>
       </c>
       <c r="AF13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH13" t="n">
         <v>12</v>
@@ -2783,10 +2850,10 @@
         <v>23</v>
       </c>
       <c r="AR13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT13" t="n">
         <v>5</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
         <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>0.806</v>
+        <v>0.8</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
@@ -2863,40 +2930,40 @@
         <v>38.8</v>
       </c>
       <c r="J14" t="n">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.481</v>
+        <v>0.48</v>
       </c>
       <c r="L14" t="n">
         <v>7.1</v>
       </c>
       <c r="M14" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0.355</v>
+        <v>0.352</v>
       </c>
       <c r="O14" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P14" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q14" t="n">
         <v>0.721</v>
       </c>
       <c r="R14" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S14" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T14" t="n">
         <v>41.7</v>
       </c>
       <c r="U14" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V14" t="n">
         <v>14.5</v>
@@ -2905,25 +2972,25 @@
         <v>10.8</v>
       </c>
       <c r="X14" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="Y14" t="n">
         <v>4.7</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>102.4</v>
+        <v>102.2</v>
       </c>
       <c r="AC14" t="n">
         <v>10.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2935,28 +3002,28 @@
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AI14" t="n">
         <v>3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK14" t="n">
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM14" t="n">
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP14" t="n">
         <v>8</v>
@@ -2983,19 +3050,19 @@
         <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY14" t="n">
         <v>9</v>
       </c>
       <c r="AZ14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BA14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>2.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
         <v>15</v>
@@ -3123,7 +3190,7 @@
         <v>14</v>
       </c>
       <c r="AJ15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK15" t="n">
         <v>9</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO15" t="n">
         <v>2</v>
@@ -3147,7 +3214,7 @@
         <v>29</v>
       </c>
       <c r="AR15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS15" t="n">
         <v>5</v>
@@ -3159,7 +3226,7 @@
         <v>19</v>
       </c>
       <c r="AV15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW15" t="n">
         <v>20</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3375,7 @@
         <v>9</v>
       </c>
       <c r="AK16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL16" t="n">
         <v>29</v>
@@ -3317,13 +3384,13 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
         <v>15</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ16" t="n">
         <v>3</v>
@@ -3335,7 +3402,7 @@
         <v>21</v>
       </c>
       <c r="AT16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU16" t="n">
         <v>20</v>
@@ -3353,7 +3420,7 @@
         <v>24</v>
       </c>
       <c r="AZ16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
         <v>11</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>4.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="n">
         <v>6</v>
@@ -3538,7 +3605,7 @@
         <v>9</v>
       </c>
       <c r="BA17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -3573,94 +3640,94 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E18" t="n">
         <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G18" t="n">
-        <v>0.552</v>
+        <v>0.571</v>
       </c>
       <c r="H18" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I18" t="n">
         <v>36.9</v>
       </c>
       <c r="J18" t="n">
-        <v>85.7</v>
+        <v>86</v>
       </c>
       <c r="K18" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L18" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M18" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.336</v>
+        <v>0.331</v>
       </c>
       <c r="O18" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="P18" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.746</v>
+        <v>0.747</v>
       </c>
       <c r="R18" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S18" t="n">
-        <v>30.5</v>
+        <v>30.8</v>
       </c>
       <c r="T18" t="n">
-        <v>42.9</v>
+        <v>43.3</v>
       </c>
       <c r="U18" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V18" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W18" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="X18" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="Y18" t="n">
         <v>4.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.5</v>
+        <v>19.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>95.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE18" t="n">
         <v>11</v>
       </c>
       <c r="AF18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH18" t="n">
         <v>19</v>
@@ -3675,10 +3742,10 @@
         <v>26</v>
       </c>
       <c r="AL18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM18" t="n">
         <v>25</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>24</v>
       </c>
       <c r="AN18" t="n">
         <v>27</v>
@@ -3687,28 +3754,28 @@
         <v>22</v>
       </c>
       <c r="AP18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ18" t="n">
         <v>20</v>
       </c>
       <c r="AR18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AT18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU18" t="n">
         <v>13</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>15</v>
       </c>
       <c r="AV18" t="n">
         <v>7</v>
       </c>
       <c r="AW18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
@@ -3720,7 +3787,7 @@
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB18" t="n">
         <v>18</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3906,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG19" t="n">
         <v>15</v>
@@ -3848,7 +3915,7 @@
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ19" t="n">
         <v>16</v>
@@ -3884,7 +3951,7 @@
         <v>2</v>
       </c>
       <c r="AU19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV19" t="n">
         <v>25</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
         <v>27</v>
@@ -4039,7 +4106,7 @@
         <v>16</v>
       </c>
       <c r="AL20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM20" t="n">
         <v>21</v>
@@ -4063,13 +4130,13 @@
         <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU20" t="n">
         <v>21</v>
       </c>
       <c r="AV20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW20" t="n">
         <v>27</v>
@@ -4081,7 +4148,7 @@
         <v>28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>5.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
         <v>4</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO21" t="n">
         <v>23</v>
@@ -4269,7 +4336,7 @@
         <v>22</v>
       </c>
       <c r="BB21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC21" t="n">
         <v>4</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -4379,10 +4446,10 @@
         <v>9</v>
       </c>
       <c r="AD22" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
         <v>1</v>
@@ -4430,13 +4497,13 @@
         <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV22" t="n">
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4448,7 +4515,7 @@
         <v>22</v>
       </c>
       <c r="BA22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-2.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
         <v>21</v>
@@ -4585,7 +4652,7 @@
         <v>11</v>
       </c>
       <c r="AL23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM23" t="n">
         <v>26</v>
@@ -4609,7 +4676,7 @@
         <v>5</v>
       </c>
       <c r="AT23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU23" t="n">
         <v>6</v>
@@ -4621,7 +4688,7 @@
         <v>29</v>
       </c>
       <c r="AX23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY23" t="n">
         <v>11</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -4743,13 +4810,13 @@
         <v>-2.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE24" t="n">
         <v>18</v>
       </c>
       <c r="AF24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG24" t="n">
         <v>20</v>
@@ -4764,7 +4831,7 @@
         <v>5</v>
       </c>
       <c r="AK24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="n">
         <v>17</v>
@@ -4773,7 +4840,7 @@
         <v>22</v>
       </c>
       <c r="AN24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO24" t="n">
         <v>29</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>23</v>
@@ -4934,7 +5001,7 @@
         <v>24</v>
       </c>
       <c r="AG25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH25" t="n">
         <v>16</v>
@@ -4976,7 +5043,7 @@
         <v>27</v>
       </c>
       <c r="AU25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
         <v>15</v>
@@ -5125,10 +5192,10 @@
         <v>20</v>
       </c>
       <c r="AJ26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL26" t="n">
         <v>7</v>
@@ -5146,7 +5213,7 @@
         <v>18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR26" t="n">
         <v>11</v>
@@ -5155,7 +5222,7 @@
         <v>26</v>
       </c>
       <c r="AT26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU26" t="n">
         <v>22</v>
@@ -5182,7 +5249,7 @@
         <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -5211,121 +5278,121 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F27" t="n">
         <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>0.367</v>
+        <v>0.345</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
       </c>
       <c r="I27" t="n">
-        <v>36.5</v>
+        <v>36.2</v>
       </c>
       <c r="J27" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K27" t="n">
-        <v>0.439</v>
+        <v>0.435</v>
       </c>
       <c r="L27" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M27" t="n">
         <v>19.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.364</v>
+        <v>0.359</v>
       </c>
       <c r="O27" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P27" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R27" t="n">
         <v>11.5</v>
       </c>
       <c r="S27" t="n">
-        <v>29.1</v>
+        <v>28.9</v>
       </c>
       <c r="T27" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="U27" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="V27" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W27" t="n">
         <v>8.1</v>
       </c>
       <c r="X27" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Z27" t="n">
         <v>21.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>96.8</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5</v>
+        <v>-5.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF27" t="n">
         <v>23</v>
       </c>
-      <c r="AF27" t="n">
-        <v>22</v>
-      </c>
       <c r="AG27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AH27" t="n">
         <v>20</v>
       </c>
       <c r="AI27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK27" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AL27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM27" t="n">
         <v>16</v>
       </c>
       <c r="AN27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO27" t="n">
         <v>19</v>
       </c>
       <c r="AP27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ27" t="n">
         <v>11</v>
@@ -5334,13 +5401,13 @@
         <v>16</v>
       </c>
       <c r="AS27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV27" t="n">
         <v>10</v>
@@ -5349,22 +5416,22 @@
         <v>9</v>
       </c>
       <c r="AX27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F28" t="n">
         <v>8</v>
       </c>
       <c r="G28" t="n">
-        <v>0.75</v>
+        <v>0.742</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
@@ -5411,43 +5478,43 @@
         <v>39.8</v>
       </c>
       <c r="J28" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.484</v>
+        <v>0.483</v>
       </c>
       <c r="L28" t="n">
         <v>8.9</v>
       </c>
       <c r="M28" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.393</v>
+        <v>0.392</v>
       </c>
       <c r="O28" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P28" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.794</v>
+        <v>0.791</v>
       </c>
       <c r="R28" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="T28" t="n">
         <v>42.1</v>
       </c>
       <c r="U28" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="V28" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W28" t="n">
         <v>8.800000000000001</v>
@@ -5456,22 +5523,22 @@
         <v>5.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>105.6</v>
+        <v>105.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5483,7 +5550,7 @@
         <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5501,22 +5568,22 @@
         <v>6</v>
       </c>
       <c r="AN28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP28" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR28" t="n">
         <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT28" t="n">
         <v>15</v>
@@ -5531,7 +5598,7 @@
         <v>5</v>
       </c>
       <c r="AX28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY28" t="n">
         <v>13</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
@@ -5662,16 +5729,16 @@
         <v>24</v>
       </c>
       <c r="AG29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK29" t="n">
         <v>24</v>
@@ -5725,7 +5792,7 @@
         <v>19</v>
       </c>
       <c r="BB29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC29" t="n">
         <v>23</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -5757,85 +5824,85 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E30" t="n">
         <v>15</v>
       </c>
       <c r="F30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G30" t="n">
-        <v>0.469</v>
+        <v>0.484</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J30" t="n">
         <v>82.3</v>
       </c>
       <c r="K30" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L30" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M30" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="O30" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="P30" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.768</v>
+        <v>0.77</v>
       </c>
       <c r="R30" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S30" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T30" t="n">
-        <v>42.8</v>
+        <v>43</v>
       </c>
       <c r="U30" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="V30" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W30" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X30" t="n">
         <v>6.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z30" t="n">
         <v>21.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.5</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
         <v>15</v>
@@ -5847,13 +5914,13 @@
         <v>18</v>
       </c>
       <c r="AH30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI30" t="n">
         <v>17</v>
       </c>
-      <c r="AI30" t="n">
-        <v>19</v>
-      </c>
       <c r="AJ30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK30" t="n">
         <v>15</v>
@@ -5862,22 +5929,22 @@
         <v>18</v>
       </c>
       <c r="AM30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO30" t="n">
         <v>5</v>
       </c>
       <c r="AP30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS30" t="n">
         <v>20</v>
@@ -5886,28 +5953,28 @@
         <v>14</v>
       </c>
       <c r="AU30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV30" t="n">
         <v>17</v>
       </c>
       <c r="AW30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ30" t="n">
         <v>27</v>
       </c>
       <c r="BA30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC30" t="n">
         <v>17</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-7.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE31" t="n">
         <v>30</v>
@@ -6035,7 +6102,7 @@
         <v>30</v>
       </c>
       <c r="AJ31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
@@ -6080,7 +6147,7 @@
         <v>22</v>
       </c>
       <c r="AY31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ31" t="n">
         <v>21</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-30-2012-13</t>
+          <t>2012-12-30</t>
         </is>
       </c>
     </row>
